--- a/artfynd/A 30846-2024 artfynd.xlsx
+++ b/artfynd/A 30846-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1467,220 +1467,6 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>112606067</v>
-      </c>
-      <c r="B9" t="n">
-        <v>78946</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Randaträsk, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>779331</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7379654</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>112606068</v>
-      </c>
-      <c r="B10" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Hydnellum ferrugineum</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Randaträsk, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>779174</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7379685</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2022-10-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
